--- a/TestData/CarDetails.xlsx
+++ b/TestData/CarDetails.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2475027\IdeaProjects\QA_warriors___Zigwheels\TestData\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,15 +36,40 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Popular Model</t>
+  </si>
+  <si>
+    <t>Maruti Suzuki Maruti 800</t>
+  </si>
+  <si>
+    <t>Maruti Suzuki Maruti Swift</t>
+  </si>
+  <si>
+    <t>Hyundai I10</t>
+  </si>
+  <si>
+    <t>Hyundai Santro Xing</t>
+  </si>
+  <si>
+    <t>Honda City</t>
+  </si>
+  <si>
+    <t>Toyota Innova</t>
+  </si>
+  <si>
+    <t>Toyota Fortuner</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -417,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B1E149-5959-4988-817E-ADF9C95F6200}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="21.6328125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -428,6 +453,46 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TestData/CarDetails.xlsx
+++ b/TestData/CarDetails.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="10">
   <si>
     <t>Popular Model</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>Mahindra XUV500</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>

--- a/TestData/CarDetails.xlsx
+++ b/TestData/CarDetails.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="10">
   <si>
     <t>Popular Model</t>
   </si>

--- a/TestData/CarDetails.xlsx
+++ b/TestData/CarDetails.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2475027\IdeaProjects\QA_warriors___Zigwheels\TestData\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,15 +36,43 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="10">
   <si>
     <t>Popular Model</t>
+  </si>
+  <si>
+    <t>Maruti Suzuki Maruti 800</t>
+  </si>
+  <si>
+    <t>Maruti Suzuki Maruti Swift</t>
+  </si>
+  <si>
+    <t>Hyundai I10</t>
+  </si>
+  <si>
+    <t>Hyundai Santro Xing</t>
+  </si>
+  <si>
+    <t>Honda City</t>
+  </si>
+  <si>
+    <t>Toyota Innova</t>
+  </si>
+  <si>
+    <t>Toyota Fortuner</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -417,10 +445,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B1E149-5959-4988-817E-ADF9C95F6200}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="21.6328125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -428,6 +456,46 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TestData/CarDetails.xlsx
+++ b/TestData/CarDetails.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="10">
   <si>
     <t>Popular Model</t>
   </si>

--- a/TestData/CarDetails.xlsx
+++ b/TestData/CarDetails.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="10">
   <si>
     <t>Popular Model</t>
   </si>

--- a/TestData/CarDetails.xlsx
+++ b/TestData/CarDetails.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="10">
   <si>
     <t>Popular Model</t>
   </si>

--- a/TestData/CarDetails.xlsx
+++ b/TestData/CarDetails.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2475027\IdeaProjects\QA_warriors___Zigwheels\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B4E156-FC9A-4077-BCC8-78611990A09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1066AB76-CCEA-4D9B-A6CB-50033561BC3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{479E8058-7C80-4673-A0CA-82749A497A58}"/>
   </bookViews>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,43 +36,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
     <t>Popular Model</t>
-  </si>
-  <si>
-    <t>Maruti Suzuki Maruti 800</t>
-  </si>
-  <si>
-    <t>Maruti Suzuki Maruti Swift</t>
-  </si>
-  <si>
-    <t>Hyundai I10</t>
-  </si>
-  <si>
-    <t>Hyundai Santro Xing</t>
-  </si>
-  <si>
-    <t>Honda City</t>
-  </si>
-  <si>
-    <t>Toyota Innova</t>
-  </si>
-  <si>
-    <t>Toyota Fortuner</t>
-  </si>
-  <si>
-    <t>Mahindra XUV500</t>
-  </si>
-  <si>
-    <t/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -445,10 +417,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B1E149-5959-4988-817E-ADF9C95F6200}">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="21.6328125"/>
+    <col min="1" max="1" width="21.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -456,46 +428,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TestData/CarDetails.xlsx
+++ b/TestData/CarDetails.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2475027\IdeaProjects\QA_warriors___Zigwheels\TestData\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,15 +36,40 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="9">
   <si>
     <t>Popular Model</t>
+  </si>
+  <si>
+    <t>Maruti Suzuki Maruti 800</t>
+  </si>
+  <si>
+    <t>Maruti Suzuki Maruti Swift</t>
+  </si>
+  <si>
+    <t>Hyundai I10</t>
+  </si>
+  <si>
+    <t>Hyundai Santro Xing</t>
+  </si>
+  <si>
+    <t>Honda City</t>
+  </si>
+  <si>
+    <t>Toyota Innova</t>
+  </si>
+  <si>
+    <t>Toyota Fortuner</t>
+  </si>
+  <si>
+    <t>Mahindra XUV500</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -417,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B1E149-5959-4988-817E-ADF9C95F6200}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="21.6328125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -428,6 +453,46 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/TestData/CarDetails.xlsx
+++ b/TestData/CarDetails.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2475027\IdeaProjects\QA_warriors___Zigwheels\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1066AB76-CCEA-4D9B-A6CB-50033561BC3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF3AE4FF-35A2-4A9F-9C8E-1A756B12DCA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{479E8058-7C80-4673-A0CA-82749A497A58}"/>
   </bookViews>
   <sheets>
-    <sheet name="CarSheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
+    <sheet name="Chennai" r:id="rId5" sheetId="6"/>
+    <sheet name="Delhi" r:id="rId6" sheetId="7"/>
+    <sheet name="Bangalore" r:id="rId7" sheetId="8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="10">
   <si>
     <t>Popular Model</t>
   </si>
@@ -63,6 +66,9 @@
   </si>
   <si>
     <t>Mahindra XUV500</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -79,18 +85,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -105,9 +105,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -441,15 +440,76 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B1E149-5959-4988-817E-ADF9C95F6200}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79C56B3D-C017-4DFE-B511-889C7641452B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="21.6328125"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
     </row>
@@ -494,6 +554,61 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/TestData/CarDetails.xlsx
+++ b/TestData/CarDetails.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="10">
   <si>
     <t>Popular Model</t>
   </si>

--- a/TestData/CarDetails.xlsx
+++ b/TestData/CarDetails.xlsx
@@ -14,6 +14,9 @@
   </bookViews>
   <sheets>
     <sheet name="CarSheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Chennai" r:id="rId5" sheetId="2"/>
+    <sheet name="Delhi" r:id="rId6" sheetId="3"/>
+    <sheet name="Bangalore" r:id="rId7" sheetId="4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="10">
   <si>
     <t>Popular Model</t>
   </si>
@@ -499,4 +502,169 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:A9"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/TestData/CarDetails.xlsx
+++ b/TestData/CarDetails.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="10">
   <si>
     <t>Popular Model</t>
   </si>
@@ -516,42 +516,42 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/CarDetails.xlsx
+++ b/TestData/CarDetails.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="10">
   <si>
     <t>Popular Model</t>
   </si>

--- a/TestData/CarDetails.xlsx
+++ b/TestData/CarDetails.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="10">
   <si>
     <t>Popular Model</t>
   </si>

--- a/TestData/CarDetails.xlsx
+++ b/TestData/CarDetails.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="10">
   <si>
     <t>Popular Model</t>
   </si>

--- a/TestData/CarDetails.xlsx
+++ b/TestData/CarDetails.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="10">
   <si>
     <t>Popular Model</t>
   </si>

--- a/TestData/CarDetails.xlsx
+++ b/TestData/CarDetails.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="10">
   <si>
     <t>Popular Model</t>
   </si>

--- a/TestData/CarDetails.xlsx
+++ b/TestData/CarDetails.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="10">
   <si>
     <t>Popular Model</t>
   </si>

--- a/TestData/CarDetails.xlsx
+++ b/TestData/CarDetails.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="10">
   <si>
     <t>Popular Model</t>
   </si>

--- a/TestData/CarDetails.xlsx
+++ b/TestData/CarDetails.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2475027\IdeaProjects\QA_warriors___Zigwheels\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B4E156-FC9A-4077-BCC8-78611990A09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD0CAB3-864E-45BD-AE5B-C840AB8B05F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{479E8058-7C80-4673-A0CA-82749A497A58}"/>
   </bookViews>
   <sheets>
-    <sheet name="CarSheet" sheetId="1" r:id="rId1"/>
-    <sheet name="Chennai" r:id="rId5" sheetId="2"/>
-    <sheet name="Delhi" r:id="rId6" sheetId="3"/>
-    <sheet name="Bangalore" r:id="rId7" sheetId="4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
+    <sheet name="Chennai" r:id="rId5" sheetId="6"/>
+    <sheet name="Delhi" r:id="rId6" sheetId="7"/>
+    <sheet name="Bangalore" r:id="rId7" sheetId="8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="9">
   <si>
     <t>Popular Model</t>
   </si>
@@ -66,9 +66,6 @@
   </si>
   <si>
     <t>Mahindra XUV500</t>
-  </si>
-  <si>
-    <t/>
   </si>
 </sst>
 </file>
@@ -85,18 +82,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -111,9 +102,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -447,64 +437,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B1E149-5959-4988-817E-ADF9C95F6200}">
-  <dimension ref="A1:A9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB3AE911-1930-4602-873B-4E3AD7B3C02A}">
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="21.6328125"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="0">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="0">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="0">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -559,7 +500,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -614,7 +555,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
